--- a/server/api/offshore_forecast_api/models/general_support_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/general_support_feature_importance.xlsx
@@ -452,62 +452,62 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.300656646490097</v>
+        <v>0.4436225891113281</v>
       </c>
       <c r="C2" t="n">
-        <v>30.06566429138184</v>
+        <v>44.36226654052734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Panjang (km)</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.138655424118042</v>
+        <v>0.2934590876102448</v>
       </c>
       <c r="C3" t="n">
-        <v>13.8655424118042</v>
+        <v>29.34591102600098</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Conductor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1132500320672989</v>
+        <v>0.07604379951953888</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3250036239624</v>
+        <v>7.60438060760498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Leg</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1118804886937141</v>
+        <v>0.05381924659013748</v>
       </c>
       <c r="C5" t="n">
-        <v>11.18804931640625</v>
+        <v>5.381925582885742</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Water Depth (meter)</t>
+          <t>Panjang (km)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1078341081738472</v>
+        <v>0.04917658120393753</v>
       </c>
       <c r="C6" t="n">
-        <v>10.78341102600098</v>
+        <v>4.917658805847168</v>
       </c>
     </row>
     <row r="7">
@@ -517,36 +517,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.10272516310215</v>
+        <v>0.03506237268447876</v>
       </c>
       <c r="C7" t="n">
-        <v>10.27251625061035</v>
+        <v>3.506237745285034</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conductor</t>
+          <t>Water Depth (meter)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06367948651313782</v>
+        <v>0.02547591924667358</v>
       </c>
       <c r="C8" t="n">
-        <v>6.367948532104492</v>
+        <v>2.547592401504517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Leg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06131867691874504</v>
+        <v>0.02334035746753216</v>
       </c>
       <c r="C9" t="n">
-        <v>6.1318678855896</v>
+        <v>2.334035873413086</v>
       </c>
     </row>
   </sheetData>
